--- a/DATA/interés para microsimular.xlsx
+++ b/DATA/interés para microsimular.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DIGEA\Desktop\IDG\IDG_2026s1\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD8A6603-B02B-495F-8DD5-80B85E7F7AEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{503B85DF-31A4-42BE-BE9B-87B60F8E2B83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -451,12 +451,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -474,14 +468,8 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -491,6 +479,18 @@
     </xf>
     <xf numFmtId="3" fontId="8" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -789,62 +789,62 @@
         <v>0</v>
       </c>
       <c r="D1" s="3"/>
-      <c r="E1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="5"/>
+      <c r="E1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="18"/>
     </row>
     <row r="2" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B2" s="6"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="8"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="6"/>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B3" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="10" t="s">
+      <c r="B3" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="9" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="13">
-        <v>1</v>
-      </c>
-      <c r="E4" s="13" t="s">
+      <c r="D4" s="10">
+        <v>1</v>
+      </c>
+      <c r="E4" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="14">
+      <c r="F4" s="11">
         <v>68358</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B5" s="12"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="13">
-        <v>2</v>
-      </c>
-      <c r="E5" s="13" t="s">
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="10">
+        <v>2</v>
+      </c>
+      <c r="E5" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="14">
+      <c r="F5" s="11">
         <v>150009</v>
       </c>
     </row>
@@ -855,56 +855,56 @@
       <c r="C6" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="16">
-        <v>1</v>
-      </c>
-      <c r="E6" s="16" t="s">
+      <c r="D6" s="12">
+        <v>1</v>
+      </c>
+      <c r="E6" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="17">
+      <c r="F6" s="13">
         <v>51020</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
-      <c r="D7" s="16">
-        <v>2</v>
-      </c>
-      <c r="E7" s="16" t="s">
+      <c r="D7" s="12">
+        <v>2</v>
+      </c>
+      <c r="E7" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="17">
+      <c r="F7" s="13">
         <v>167347</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="13">
-        <v>1</v>
-      </c>
-      <c r="E8" s="13" t="s">
+      <c r="D8" s="10">
+        <v>1</v>
+      </c>
+      <c r="E8" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="14">
+      <c r="F8" s="11">
         <v>52107</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="13">
-        <v>2</v>
-      </c>
-      <c r="E9" s="13" t="s">
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="10">
+        <v>2</v>
+      </c>
+      <c r="E9" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="14">
+      <c r="F9" s="11">
         <v>166260</v>
       </c>
     </row>
@@ -915,56 +915,56 @@
       <c r="C10" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="16">
-        <v>1</v>
-      </c>
-      <c r="E10" s="16" t="s">
+      <c r="D10" s="12">
+        <v>1</v>
+      </c>
+      <c r="E10" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="F10" s="17">
+      <c r="F10" s="13">
         <v>24106</v>
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B11" s="15"/>
       <c r="C11" s="15"/>
-      <c r="D11" s="16">
-        <v>2</v>
-      </c>
-      <c r="E11" s="16" t="s">
+      <c r="D11" s="12">
+        <v>2</v>
+      </c>
+      <c r="E11" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F11" s="17">
+      <c r="F11" s="13">
         <v>194261</v>
       </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="13">
-        <v>1</v>
-      </c>
-      <c r="E12" s="13" t="s">
+      <c r="D12" s="10">
+        <v>1</v>
+      </c>
+      <c r="E12" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F12" s="14">
+      <c r="F12" s="11">
         <v>34494</v>
       </c>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="13">
-        <v>2</v>
-      </c>
-      <c r="E13" s="13" t="s">
+      <c r="B13" s="16"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="10">
+        <v>2</v>
+      </c>
+      <c r="E13" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="F13" s="14">
+      <c r="F13" s="11">
         <v>183873</v>
       </c>
     </row>
@@ -975,56 +975,56 @@
       <c r="C14" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="16">
-        <v>1</v>
-      </c>
-      <c r="E14" s="16" t="s">
+      <c r="D14" s="12">
+        <v>1</v>
+      </c>
+      <c r="E14" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="F14" s="17">
+      <c r="F14" s="13">
         <v>19693</v>
       </c>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B15" s="15"/>
       <c r="C15" s="15"/>
-      <c r="D15" s="16">
-        <v>2</v>
-      </c>
-      <c r="E15" s="16" t="s">
+      <c r="D15" s="12">
+        <v>2</v>
+      </c>
+      <c r="E15" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F15" s="17">
+      <c r="F15" s="13">
         <v>198674</v>
       </c>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B16" s="12" t="s">
+      <c r="B16" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="D16" s="13">
-        <v>1</v>
-      </c>
-      <c r="E16" s="13" t="s">
+      <c r="D16" s="10">
+        <v>1</v>
+      </c>
+      <c r="E16" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F16" s="14">
+      <c r="F16" s="11">
         <v>19104</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B17" s="12"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="13">
-        <v>2</v>
-      </c>
-      <c r="E17" s="13" t="s">
+      <c r="B17" s="16"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="10">
+        <v>2</v>
+      </c>
+      <c r="E17" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="F17" s="14">
+      <c r="F17" s="11">
         <v>199263</v>
       </c>
     </row>
@@ -1035,138 +1035,138 @@
       <c r="C18" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="16">
-        <v>1</v>
-      </c>
-      <c r="E18" s="16" t="s">
+      <c r="D18" s="12">
+        <v>1</v>
+      </c>
+      <c r="E18" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="F18" s="17">
+      <c r="F18" s="13">
         <v>11031</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B19" s="15"/>
       <c r="C19" s="15"/>
-      <c r="D19" s="16">
-        <v>2</v>
-      </c>
-      <c r="E19" s="16" t="s">
+      <c r="D19" s="12">
+        <v>2</v>
+      </c>
+      <c r="E19" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F19" s="17">
+      <c r="F19" s="13">
         <v>207336</v>
       </c>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="D20" s="13">
+      <c r="D20" s="10">
         <v>-99</v>
       </c>
-      <c r="E20" s="13" t="s">
+      <c r="E20" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="F20" s="14">
+      <c r="F20" s="11">
         <v>59</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="13">
+      <c r="B21" s="16"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="10">
         <v>-88</v>
       </c>
-      <c r="E21" s="13" t="s">
+      <c r="E21" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="F21" s="14">
+      <c r="F21" s="11">
         <v>123</v>
       </c>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B22" s="12"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="13">
-        <v>1</v>
-      </c>
-      <c r="E22" s="13" t="s">
+      <c r="B22" s="16"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="10">
+        <v>1</v>
+      </c>
+      <c r="E22" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F22" s="14">
+      <c r="F22" s="11">
         <v>5110</v>
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B23" s="12"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="13">
-        <v>2</v>
-      </c>
-      <c r="E23" s="13" t="s">
+      <c r="B23" s="16"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="10">
+        <v>2</v>
+      </c>
+      <c r="E23" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="F23" s="14">
+      <c r="F23" s="11">
         <v>185364</v>
       </c>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B24" s="12" t="s">
+      <c r="B24" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="C24" s="12" t="s">
+      <c r="C24" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="D24" s="13">
+      <c r="D24" s="10">
         <v>-99</v>
       </c>
-      <c r="E24" s="13" t="s">
+      <c r="E24" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="F24" s="14">
+      <c r="F24" s="11">
         <v>35</v>
       </c>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B25" s="12"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="13">
+      <c r="B25" s="16"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="10">
         <v>-88</v>
       </c>
-      <c r="E25" s="13" t="s">
+      <c r="E25" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="F25" s="14">
+      <c r="F25" s="11">
         <v>205</v>
       </c>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B26" s="12"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="13">
-        <v>1</v>
-      </c>
-      <c r="E26" s="13" t="s">
+      <c r="B26" s="16"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="10">
+        <v>1</v>
+      </c>
+      <c r="E26" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F26" s="14">
+      <c r="F26" s="11">
         <v>388</v>
       </c>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B27" s="12"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="13">
-        <v>2</v>
-      </c>
-      <c r="E27" s="13" t="s">
+      <c r="B27" s="16"/>
+      <c r="C27" s="16"/>
+      <c r="D27" s="10">
+        <v>2</v>
+      </c>
+      <c r="E27" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="F27" s="14">
+      <c r="F27" s="11">
         <v>190028</v>
       </c>
     </row>
@@ -1177,91 +1177,91 @@
       <c r="C28" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="D28" s="16">
+      <c r="D28" s="12">
         <v>-88</v>
       </c>
-      <c r="E28" s="16" t="s">
+      <c r="E28" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="F28" s="17">
+      <c r="F28" s="13">
         <v>247</v>
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B29" s="15"/>
       <c r="C29" s="15"/>
-      <c r="D29" s="16">
-        <v>1</v>
-      </c>
-      <c r="E29" s="16" t="s">
+      <c r="D29" s="12">
+        <v>1</v>
+      </c>
+      <c r="E29" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="F29" s="17">
+      <c r="F29" s="13">
         <v>70509</v>
       </c>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B30" s="15"/>
       <c r="C30" s="15"/>
-      <c r="D30" s="16">
-        <v>2</v>
-      </c>
-      <c r="E30" s="16" t="s">
+      <c r="D30" s="12">
+        <v>2</v>
+      </c>
+      <c r="E30" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="F30" s="17">
+      <c r="F30" s="13">
         <v>969</v>
       </c>
     </row>
     <row r="31" spans="2:6" ht="30" x14ac:dyDescent="0.25">
       <c r="B31" s="15"/>
       <c r="C31" s="15"/>
-      <c r="D31" s="16">
+      <c r="D31" s="12">
         <v>3</v>
       </c>
-      <c r="E31" s="16" t="s">
+      <c r="E31" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="F31" s="17">
+      <c r="F31" s="13">
         <v>762</v>
       </c>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B32" s="15"/>
       <c r="C32" s="15"/>
-      <c r="D32" s="16">
+      <c r="D32" s="12">
         <v>4</v>
       </c>
-      <c r="E32" s="16" t="s">
+      <c r="E32" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="F32" s="17">
+      <c r="F32" s="13">
         <v>645</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B33" s="15"/>
       <c r="C33" s="15"/>
-      <c r="D33" s="16">
+      <c r="D33" s="12">
         <v>5</v>
       </c>
-      <c r="E33" s="16" t="s">
+      <c r="E33" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="F33" s="17">
+      <c r="F33" s="13">
         <v>7</v>
       </c>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B34" s="15"/>
       <c r="C34" s="15"/>
-      <c r="D34" s="16">
+      <c r="D34" s="12">
         <v>6</v>
       </c>
-      <c r="E34" s="16" t="s">
+      <c r="E34" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="F34" s="17">
+      <c r="F34" s="13">
         <v>56432</v>
       </c>
     </row>
@@ -1272,104 +1272,104 @@
       <c r="C35" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="D35" s="16">
-        <v>1</v>
-      </c>
-      <c r="E35" s="16" t="s">
+      <c r="D35" s="12">
+        <v>1</v>
+      </c>
+      <c r="E35" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="F35" s="18">
+      <c r="F35" s="14">
         <v>54575</v>
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B36" s="15"/>
       <c r="C36" s="15"/>
-      <c r="D36" s="16">
-        <v>2</v>
-      </c>
-      <c r="E36" s="16" t="s">
+      <c r="D36" s="12">
+        <v>2</v>
+      </c>
+      <c r="E36" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="F36" s="18">
+      <c r="F36" s="14">
         <v>33153</v>
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B37" s="15"/>
       <c r="C37" s="15"/>
-      <c r="D37" s="16">
+      <c r="D37" s="12">
         <v>3</v>
       </c>
-      <c r="E37" s="16" t="s">
+      <c r="E37" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="F37" s="18">
+      <c r="F37" s="14">
         <v>752</v>
       </c>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B38" s="15"/>
       <c r="C38" s="15"/>
-      <c r="D38" s="16">
+      <c r="D38" s="12">
         <v>4</v>
       </c>
-      <c r="E38" s="16" t="s">
+      <c r="E38" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="F38" s="18">
+      <c r="F38" s="14">
         <v>167</v>
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B39" s="15"/>
       <c r="C39" s="15"/>
-      <c r="D39" s="16">
+      <c r="D39" s="12">
         <v>5</v>
       </c>
-      <c r="E39" s="16" t="s">
+      <c r="E39" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="F39" s="18">
+      <c r="F39" s="14">
         <v>7534</v>
       </c>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B40" s="15"/>
       <c r="C40" s="15"/>
-      <c r="D40" s="16">
+      <c r="D40" s="12">
         <v>6</v>
       </c>
-      <c r="E40" s="16" t="s">
+      <c r="E40" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="F40" s="18">
+      <c r="F40" s="14">
         <v>5815</v>
       </c>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B41" s="15"/>
       <c r="C41" s="15"/>
-      <c r="D41" s="16">
+      <c r="D41" s="12">
         <v>7</v>
       </c>
-      <c r="E41" s="16" t="s">
+      <c r="E41" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="F41" s="18">
+      <c r="F41" s="14">
         <v>10864</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B42" s="15"/>
       <c r="C42" s="15"/>
-      <c r="D42" s="16">
+      <c r="D42" s="12">
         <v>8</v>
       </c>
-      <c r="E42" s="16" t="s">
+      <c r="E42" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="F42" s="18">
+      <c r="F42" s="14">
         <v>71768</v>
       </c>
     </row>
@@ -1380,78 +1380,78 @@
       <c r="C43" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="D43" s="16">
+      <c r="D43" s="12">
         <v>-88</v>
       </c>
-      <c r="E43" s="16" t="s">
+      <c r="E43" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="F43" s="17">
+      <c r="F43" s="13">
         <v>670</v>
       </c>
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B44" s="15"/>
       <c r="C44" s="15"/>
-      <c r="D44" s="16">
-        <v>1</v>
-      </c>
-      <c r="E44" s="16" t="s">
+      <c r="D44" s="12">
+        <v>1</v>
+      </c>
+      <c r="E44" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="F44" s="17">
+      <c r="F44" s="13">
         <v>189695</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B45" s="15"/>
       <c r="C45" s="15"/>
-      <c r="D45" s="16">
-        <v>2</v>
-      </c>
-      <c r="E45" s="16" t="s">
+      <c r="D45" s="12">
+        <v>2</v>
+      </c>
+      <c r="E45" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="F45" s="17">
+      <c r="F45" s="13">
         <v>19306</v>
       </c>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B46" s="15"/>
       <c r="C46" s="15"/>
-      <c r="D46" s="16">
+      <c r="D46" s="12">
         <v>3</v>
       </c>
-      <c r="E46" s="16" t="s">
+      <c r="E46" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="F46" s="17">
+      <c r="F46" s="13">
         <v>4089</v>
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B47" s="15"/>
       <c r="C47" s="15"/>
-      <c r="D47" s="16">
+      <c r="D47" s="12">
         <v>4</v>
       </c>
-      <c r="E47" s="16" t="s">
+      <c r="E47" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="F47" s="17">
+      <c r="F47" s="13">
         <v>4203</v>
       </c>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B48" s="15"/>
       <c r="C48" s="15"/>
-      <c r="D48" s="16">
+      <c r="D48" s="12">
         <v>5</v>
       </c>
-      <c r="E48" s="16" t="s">
+      <c r="E48" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="F48" s="17">
+      <c r="F48" s="13">
         <v>404</v>
       </c>
     </row>
@@ -1462,52 +1462,52 @@
       <c r="C49" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="D49" s="16">
+      <c r="D49" s="12">
         <v>-88</v>
       </c>
-      <c r="E49" s="16" t="s">
+      <c r="E49" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="F49" s="17">
+      <c r="F49" s="13">
         <v>14</v>
       </c>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B50" s="15"/>
       <c r="C50" s="15"/>
-      <c r="D50" s="16">
-        <v>1</v>
-      </c>
-      <c r="E50" s="16" t="s">
+      <c r="D50" s="12">
+        <v>1</v>
+      </c>
+      <c r="E50" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="F50" s="17">
+      <c r="F50" s="13">
         <v>36818</v>
       </c>
     </row>
     <row r="51" spans="2:6" ht="30" x14ac:dyDescent="0.25">
       <c r="B51" s="15"/>
       <c r="C51" s="15"/>
-      <c r="D51" s="16">
-        <v>2</v>
-      </c>
-      <c r="E51" s="16" t="s">
+      <c r="D51" s="12">
+        <v>2</v>
+      </c>
+      <c r="E51" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="F51" s="17">
+      <c r="F51" s="13">
         <v>18122</v>
       </c>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B52" s="15"/>
       <c r="C52" s="15"/>
-      <c r="D52" s="16">
+      <c r="D52" s="12">
         <v>3</v>
       </c>
-      <c r="E52" s="16" t="s">
+      <c r="E52" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="F52" s="17">
+      <c r="F52" s="13">
         <v>471</v>
       </c>
     </row>
@@ -1518,52 +1518,52 @@
       <c r="C53" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="D53" s="16">
+      <c r="D53" s="12">
         <v>-88</v>
       </c>
-      <c r="E53" s="16" t="s">
+      <c r="E53" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="F53" s="17">
+      <c r="F53" s="13">
         <v>38</v>
       </c>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B54" s="15"/>
       <c r="C54" s="15"/>
-      <c r="D54" s="16">
-        <v>1</v>
-      </c>
-      <c r="E54" s="16" t="s">
+      <c r="D54" s="12">
+        <v>1</v>
+      </c>
+      <c r="E54" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="F54" s="17">
+      <c r="F54" s="13">
         <v>90107</v>
       </c>
     </row>
     <row r="55" spans="2:6" ht="30" x14ac:dyDescent="0.25">
       <c r="B55" s="15"/>
       <c r="C55" s="15"/>
-      <c r="D55" s="16">
-        <v>2</v>
-      </c>
-      <c r="E55" s="16" t="s">
+      <c r="D55" s="12">
+        <v>2</v>
+      </c>
+      <c r="E55" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="F55" s="17">
+      <c r="F55" s="13">
         <v>39508</v>
       </c>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B56" s="15"/>
       <c r="C56" s="15"/>
-      <c r="D56" s="16">
+      <c r="D56" s="12">
         <v>3</v>
       </c>
-      <c r="E56" s="16" t="s">
+      <c r="E56" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="F56" s="17">
+      <c r="F56" s="13">
         <v>1508</v>
       </c>
     </row>
@@ -1574,78 +1574,78 @@
       <c r="C57" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="D57" s="16">
-        <v>1</v>
-      </c>
-      <c r="E57" s="16" t="s">
+      <c r="D57" s="12">
+        <v>1</v>
+      </c>
+      <c r="E57" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="F57" s="17">
+      <c r="F57" s="13">
         <v>4125</v>
       </c>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B58" s="15"/>
       <c r="C58" s="15"/>
-      <c r="D58" s="16">
-        <v>2</v>
-      </c>
-      <c r="E58" s="16" t="s">
+      <c r="D58" s="12">
+        <v>2</v>
+      </c>
+      <c r="E58" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="F58" s="17">
+      <c r="F58" s="13">
         <v>16085</v>
       </c>
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B59" s="15"/>
       <c r="C59" s="15"/>
-      <c r="D59" s="16">
+      <c r="D59" s="12">
         <v>3</v>
       </c>
-      <c r="E59" s="16" t="s">
+      <c r="E59" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="F59" s="17">
+      <c r="F59" s="13">
         <v>18224</v>
       </c>
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B60" s="15"/>
       <c r="C60" s="15"/>
-      <c r="D60" s="16">
+      <c r="D60" s="12">
         <v>4</v>
       </c>
-      <c r="E60" s="16" t="s">
+      <c r="E60" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="F60" s="17">
+      <c r="F60" s="13">
         <v>1538</v>
       </c>
     </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B61" s="15"/>
       <c r="C61" s="15"/>
-      <c r="D61" s="16">
+      <c r="D61" s="12">
         <v>5</v>
       </c>
-      <c r="E61" s="16" t="s">
+      <c r="E61" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="F61" s="17">
+      <c r="F61" s="13">
         <v>2089</v>
       </c>
     </row>
     <row r="62" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B62" s="15"/>
       <c r="C62" s="15"/>
-      <c r="D62" s="16">
+      <c r="D62" s="12">
         <v>6</v>
       </c>
-      <c r="E62" s="16" t="s">
+      <c r="E62" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="F62" s="17">
+      <c r="F62" s="13">
         <v>35833</v>
       </c>
     </row>
@@ -1656,108 +1656,108 @@
       <c r="C63" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="D63" s="16">
-        <v>1</v>
-      </c>
-      <c r="E63" s="16" t="s">
+      <c r="D63" s="12">
+        <v>1</v>
+      </c>
+      <c r="E63" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="F63" s="17">
+      <c r="F63" s="13">
         <v>152265</v>
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B64" s="15"/>
       <c r="C64" s="15"/>
-      <c r="D64" s="16">
-        <v>2</v>
-      </c>
-      <c r="E64" s="16" t="s">
+      <c r="D64" s="12">
+        <v>2</v>
+      </c>
+      <c r="E64" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F64" s="17">
+      <c r="F64" s="13">
         <v>43489</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B65" s="15"/>
       <c r="C65" s="15"/>
-      <c r="D65" s="16">
+      <c r="D65" s="12">
         <v>3</v>
       </c>
-      <c r="E65" s="16" t="s">
+      <c r="E65" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="F65" s="17">
+      <c r="F65" s="13">
         <v>16107</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B66" s="15"/>
       <c r="C66" s="15"/>
-      <c r="D66" s="16">
+      <c r="D66" s="12">
         <v>4</v>
       </c>
-      <c r="E66" s="16" t="s">
+      <c r="E66" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="F66" s="17">
+      <c r="F66" s="13">
         <v>6506</v>
       </c>
     </row>
     <row r="67" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B67" s="12" t="s">
+      <c r="B67" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="C67" s="12" t="s">
+      <c r="C67" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="D67" s="13">
-        <v>1</v>
-      </c>
-      <c r="E67" s="13" t="s">
+      <c r="D67" s="10">
+        <v>1</v>
+      </c>
+      <c r="E67" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="F67" s="14">
+      <c r="F67" s="11">
         <v>96259</v>
       </c>
     </row>
     <row r="68" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B68" s="12"/>
-      <c r="C68" s="12"/>
-      <c r="D68" s="13">
-        <v>2</v>
-      </c>
-      <c r="E68" s="13" t="s">
+      <c r="B68" s="16"/>
+      <c r="C68" s="16"/>
+      <c r="D68" s="10">
+        <v>2</v>
+      </c>
+      <c r="E68" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="F68" s="14">
+      <c r="F68" s="11">
         <v>50223</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B69" s="12"/>
-      <c r="C69" s="12"/>
-      <c r="D69" s="13">
+      <c r="B69" s="16"/>
+      <c r="C69" s="16"/>
+      <c r="D69" s="10">
         <v>3</v>
       </c>
-      <c r="E69" s="13" t="s">
+      <c r="E69" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="F69" s="14">
+      <c r="F69" s="11">
         <v>43707</v>
       </c>
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B70" s="12"/>
-      <c r="C70" s="12"/>
-      <c r="D70" s="13">
+      <c r="B70" s="16"/>
+      <c r="C70" s="16"/>
+      <c r="D70" s="10">
         <v>4</v>
       </c>
-      <c r="E70" s="13" t="s">
+      <c r="E70" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="F70" s="14">
+      <c r="F70" s="11">
         <v>28178</v>
       </c>
     </row>
@@ -1768,108 +1768,108 @@
       <c r="C71" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="D71" s="16">
-        <v>1</v>
-      </c>
-      <c r="E71" s="16" t="s">
+      <c r="D71" s="12">
+        <v>1</v>
+      </c>
+      <c r="E71" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="F71" s="17">
+      <c r="F71" s="13">
         <v>147566</v>
       </c>
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B72" s="15"/>
       <c r="C72" s="15"/>
-      <c r="D72" s="16">
-        <v>2</v>
-      </c>
-      <c r="E72" s="16" t="s">
+      <c r="D72" s="12">
+        <v>2</v>
+      </c>
+      <c r="E72" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F72" s="17">
+      <c r="F72" s="13">
         <v>32349</v>
       </c>
     </row>
     <row r="73" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B73" s="15"/>
       <c r="C73" s="15"/>
-      <c r="D73" s="16">
+      <c r="D73" s="12">
         <v>3</v>
       </c>
-      <c r="E73" s="16" t="s">
+      <c r="E73" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="F73" s="17">
+      <c r="F73" s="13">
         <v>23267</v>
       </c>
     </row>
     <row r="74" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B74" s="15"/>
       <c r="C74" s="15"/>
-      <c r="D74" s="16">
+      <c r="D74" s="12">
         <v>4</v>
       </c>
-      <c r="E74" s="16" t="s">
+      <c r="E74" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="F74" s="17">
+      <c r="F74" s="13">
         <v>15185</v>
       </c>
     </row>
     <row r="75" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B75" s="12" t="s">
+      <c r="B75" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="C75" s="12" t="s">
+      <c r="C75" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="D75" s="13">
-        <v>1</v>
-      </c>
-      <c r="E75" s="13" t="s">
+      <c r="D75" s="10">
+        <v>1</v>
+      </c>
+      <c r="E75" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="F75" s="14">
+      <c r="F75" s="11">
         <v>136214</v>
       </c>
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B76" s="12"/>
-      <c r="C76" s="12"/>
-      <c r="D76" s="13">
-        <v>2</v>
-      </c>
-      <c r="E76" s="13" t="s">
+      <c r="B76" s="16"/>
+      <c r="C76" s="16"/>
+      <c r="D76" s="10">
+        <v>2</v>
+      </c>
+      <c r="E76" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="F76" s="14">
+      <c r="F76" s="11">
         <v>48909</v>
       </c>
     </row>
     <row r="77" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B77" s="12"/>
-      <c r="C77" s="12"/>
-      <c r="D77" s="13">
+      <c r="B77" s="16"/>
+      <c r="C77" s="16"/>
+      <c r="D77" s="10">
         <v>3</v>
       </c>
-      <c r="E77" s="13" t="s">
+      <c r="E77" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="F77" s="14">
+      <c r="F77" s="11">
         <v>22365</v>
       </c>
     </row>
     <row r="78" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B78" s="12"/>
-      <c r="C78" s="12"/>
-      <c r="D78" s="13">
+      <c r="B78" s="16"/>
+      <c r="C78" s="16"/>
+      <c r="D78" s="10">
         <v>4</v>
       </c>
-      <c r="E78" s="13" t="s">
+      <c r="E78" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="F78" s="14">
+      <c r="F78" s="11">
         <v>10879</v>
       </c>
     </row>
@@ -1880,100 +1880,100 @@
       <c r="C79" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="D79" s="16">
-        <v>1</v>
-      </c>
-      <c r="E79" s="16" t="s">
+      <c r="D79" s="12">
+        <v>1</v>
+      </c>
+      <c r="E79" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="F79" s="17">
+      <c r="F79" s="13">
         <v>143958</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B80" s="15"/>
       <c r="C80" s="15"/>
-      <c r="D80" s="16">
-        <v>2</v>
-      </c>
-      <c r="E80" s="16" t="s">
+      <c r="D80" s="12">
+        <v>2</v>
+      </c>
+      <c r="E80" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F80" s="17">
+      <c r="F80" s="13">
         <v>44425</v>
       </c>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B81" s="15"/>
       <c r="C81" s="15"/>
-      <c r="D81" s="16">
+      <c r="D81" s="12">
         <v>3</v>
       </c>
-      <c r="E81" s="16" t="s">
+      <c r="E81" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="F81" s="17">
+      <c r="F81" s="13">
         <v>19180</v>
       </c>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B82" s="15"/>
       <c r="C82" s="15"/>
-      <c r="D82" s="16">
+      <c r="D82" s="12">
         <v>4</v>
       </c>
-      <c r="E82" s="16" t="s">
+      <c r="E82" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="F82" s="17">
+      <c r="F82" s="13">
         <v>10804</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="43">
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="B20:B23"/>
+    <mergeCell ref="C20:C23"/>
+    <mergeCell ref="B24:B27"/>
+    <mergeCell ref="C24:C27"/>
+    <mergeCell ref="C28:C34"/>
+    <mergeCell ref="B28:B34"/>
+    <mergeCell ref="B35:B42"/>
+    <mergeCell ref="C35:C42"/>
+    <mergeCell ref="B43:B48"/>
+    <mergeCell ref="C43:C48"/>
+    <mergeCell ref="B49:B52"/>
+    <mergeCell ref="C49:C52"/>
+    <mergeCell ref="B53:B56"/>
+    <mergeCell ref="C53:C56"/>
+    <mergeCell ref="B57:B62"/>
+    <mergeCell ref="C57:C62"/>
+    <mergeCell ref="B63:B66"/>
+    <mergeCell ref="C63:C66"/>
+    <mergeCell ref="B67:B70"/>
+    <mergeCell ref="C67:C70"/>
     <mergeCell ref="B71:B74"/>
     <mergeCell ref="C71:C74"/>
     <mergeCell ref="B75:B78"/>
     <mergeCell ref="C75:C78"/>
     <mergeCell ref="B79:B82"/>
     <mergeCell ref="C79:C82"/>
-    <mergeCell ref="B57:B62"/>
-    <mergeCell ref="C57:C62"/>
-    <mergeCell ref="B63:B66"/>
-    <mergeCell ref="C63:C66"/>
-    <mergeCell ref="B67:B70"/>
-    <mergeCell ref="C67:C70"/>
-    <mergeCell ref="B43:B48"/>
-    <mergeCell ref="C43:C48"/>
-    <mergeCell ref="B49:B52"/>
-    <mergeCell ref="C49:C52"/>
-    <mergeCell ref="B53:B56"/>
-    <mergeCell ref="C53:C56"/>
-    <mergeCell ref="B24:B27"/>
-    <mergeCell ref="C24:C27"/>
-    <mergeCell ref="C28:C34"/>
-    <mergeCell ref="B28:B34"/>
-    <mergeCell ref="B35:B42"/>
-    <mergeCell ref="C35:C42"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="B20:B23"/>
-    <mergeCell ref="C20:C23"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
